--- a/Data/Config_Test.xlsx
+++ b/Data/Config_Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github.com\rpapub\PurposefulPromethium\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{549F1927-F52B-437D-AE6E-A1BD6463E64D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0100A785-6A4F-48BE-9BC3-6DCFD24E775B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1230" yWindow="3720" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4230" yWindow="2925" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="65">
   <si>
     <t>Name</t>
   </si>
@@ -211,6 +211,15 @@
   </si>
   <si>
     <t>.\Data\Temp\ACME</t>
+  </si>
+  <si>
+    <t>WebApp_ChallengeStarted</t>
+  </si>
+  <si>
+    <t>Mailbox_BatchsizeActual</t>
+  </si>
+  <si>
+    <t>Target_Batchsize</t>
   </si>
 </sst>
 </file>
@@ -262,7 +271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -273,6 +282,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -589,7 +602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1003"/>
+  <dimension ref="A1:Z1005"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.5703125" customWidth="1"/>
@@ -703,103 +716,118 @@
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>39</v>
+      <c r="A13" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="7">
+        <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="5">
-        <v>10</v>
-      </c>
-    </row>
+    <row r="14" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
+      </c>
+      <c r="C15" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>44</v>
+        <v>34</v>
+      </c>
+      <c r="B16" s="5">
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.25" customHeight="1">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="18" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
     <row r="19" spans="1:2" ht="14.25" customHeight="1">
       <c r="A19" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="21" spans="1:2" ht="14.25" customHeight="1">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A22" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" s="5">
-        <v>21</v>
-      </c>
-    </row>
+    <row r="22" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="23" spans="1:2" ht="14.25" customHeight="1">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="14.25" customHeight="1">
       <c r="A24" t="s">
-        <v>53</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>50</v>
+        <v>45</v>
+      </c>
+      <c r="B24" s="5">
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="14.25" customHeight="1">
       <c r="A25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A27" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B27" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="27" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="28" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="29" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="30" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="29" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A29" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A30" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
     <row r="31" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="32" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="33" ht="14.25" customHeight="1"/>
@@ -1773,6 +1801,8 @@
     <row r="1001" ht="14.25" customHeight="1"/>
     <row r="1002" ht="14.25" customHeight="1"/>
     <row r="1003" ht="14.25" customHeight="1"/>
+    <row r="1004" ht="14.25" customHeight="1"/>
+    <row r="1005" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Config_Test.xlsx
+++ b/Data/Config_Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github.com\rpapub\PurposefulPromethium\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0100A785-6A4F-48BE-9BC3-6DCFD24E775B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94BE2D46-EB0A-4794-AABE-731D7779788D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4230" yWindow="2925" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1095" yWindow="3540" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="70">
   <si>
     <t>Name</t>
   </si>
@@ -132,9 +132,6 @@
     <t>Mailbox_Batchsize</t>
   </si>
   <si>
-    <t>INBOX/TEST_ACME</t>
-  </si>
-  <si>
     <t>Imap_Credentialname</t>
   </si>
   <si>
@@ -147,21 +144,12 @@
     <t>The folder in development environment. In prod env will be RPA/PurposefulPromethium/incoming</t>
   </si>
   <si>
-    <t>RPA/PurposefulPromethium/processing</t>
-  </si>
-  <si>
     <t>Mailbox_FolderSuccessful</t>
   </si>
   <si>
     <t>Mailbox_FolderHandover2Human</t>
   </si>
   <si>
-    <t>RPA/PurposefulPromethium/successful</t>
-  </si>
-  <si>
-    <t>RPA/PurposefulPromethium/handover2human</t>
-  </si>
-  <si>
     <t>FTP_ServerPort</t>
   </si>
   <si>
@@ -177,9 +165,6 @@
     <t>10.23.11.1</t>
   </si>
   <si>
-    <t>ACME</t>
-  </si>
-  <si>
     <t>FTP_RemotePathTainted</t>
   </si>
   <si>
@@ -220,6 +205,36 @@
   </si>
   <si>
     <t>Target_Batchsize</t>
+  </si>
+  <si>
+    <t>ACME/Testing</t>
+  </si>
+  <si>
+    <t>RPA/PurposefulPromethium/Testing/EndToEnd</t>
+  </si>
+  <si>
+    <t>Mailbox_FolderSuccessfulFormatA</t>
+  </si>
+  <si>
+    <t>Mailbox_FolderSuccessfulFormatB</t>
+  </si>
+  <si>
+    <t>False</t>
+  </si>
+  <si>
+    <t>RPA/PurposefulPromethium/Testing/EndToEnd/successful</t>
+  </si>
+  <si>
+    <t>RPA/PurposefulPromethium/Testing/EndToEnd/handover2human</t>
+  </si>
+  <si>
+    <t>RPA/PurposefulPromethium/Testing/EndToEnd/incoming</t>
+  </si>
+  <si>
+    <t>RPA/PurposefulPromethium/Testing/EndToEnd/successful/FormatA</t>
+  </si>
+  <si>
+    <t>RPA/PurposefulPromethium/Testing/EndToEnd/successful/FormatB</t>
   </si>
 </sst>
 </file>
@@ -271,7 +286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -287,6 +302,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -602,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1005"/>
+  <dimension ref="A1:Z1008"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.5703125" customWidth="1"/>
@@ -658,10 +676,10 @@
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C3" s="2"/>
     </row>
@@ -671,7 +689,7 @@
         <v>26</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>29</v>
@@ -680,13 +698,13 @@
     <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1"/>
@@ -708,16 +726,16 @@
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
       <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B13" s="7">
         <v>10</v>
@@ -728,11 +746,11 @@
       <c r="A15" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>35</v>
+      <c r="B15" s="8" t="s">
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
@@ -740,112 +758,134 @@
         <v>34</v>
       </c>
       <c r="B16" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>40</v>
+    <row r="17" spans="1:2" s="6" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A17" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="14.25" customHeight="1">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.25" customHeight="1">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="21" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A21" t="s">
-        <v>60</v>
+    <row r="20" spans="1:2" s="6" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A20" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" s="6" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A21" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="23" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A23" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>49</v>
+    <row r="22" spans="1:2" s="6" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A22" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>69</v>
       </c>
     </row>
+    <row r="23" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="24" spans="1:2" ht="14.25" customHeight="1">
       <c r="A24" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="5">
-        <v>21</v>
+        <v>55</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A25" t="s">
-        <v>47</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
+    <row r="25" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="26" spans="1:2" ht="14.25" customHeight="1">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="14.25" customHeight="1">
       <c r="A27" t="s">
-        <v>51</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>52</v>
+        <v>41</v>
+      </c>
+      <c r="B27" s="5">
+        <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="28" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A28" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
     <row r="29" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A29" s="6" t="s">
-        <v>62</v>
+      <c r="A29" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A30" s="6" t="s">
-        <v>63</v>
+      <c r="A30" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="32" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="33" ht="14.25" customHeight="1"/>
-    <row r="34" ht="14.25" customHeight="1"/>
-    <row r="35" ht="14.25" customHeight="1"/>
-    <row r="36" ht="14.25" customHeight="1"/>
-    <row r="37" ht="14.25" customHeight="1"/>
-    <row r="38" ht="14.25" customHeight="1"/>
-    <row r="39" ht="14.25" customHeight="1"/>
-    <row r="40" ht="14.25" customHeight="1"/>
-    <row r="41" ht="14.25" customHeight="1"/>
-    <row r="42" ht="14.25" customHeight="1"/>
-    <row r="43" ht="14.25" customHeight="1"/>
-    <row r="44" ht="14.25" customHeight="1"/>
-    <row r="45" ht="14.25" customHeight="1"/>
-    <row r="46" ht="14.25" customHeight="1"/>
-    <row r="47" ht="14.25" customHeight="1"/>
-    <row r="48" ht="14.25" customHeight="1"/>
+    <row r="32" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A32" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="14.25" customHeight="1">
+      <c r="A33" s="6"/>
+    </row>
+    <row r="34" spans="1:1" ht="14.25" customHeight="1"/>
+    <row r="35" spans="1:1" ht="14.25" customHeight="1"/>
+    <row r="36" spans="1:1" ht="14.25" customHeight="1"/>
+    <row r="37" spans="1:1" ht="14.25" customHeight="1"/>
+    <row r="38" spans="1:1" ht="14.25" customHeight="1"/>
+    <row r="39" spans="1:1" ht="14.25" customHeight="1"/>
+    <row r="40" spans="1:1" ht="14.25" customHeight="1"/>
+    <row r="41" spans="1:1" ht="14.25" customHeight="1"/>
+    <row r="42" spans="1:1" ht="14.25" customHeight="1"/>
+    <row r="43" spans="1:1" ht="14.25" customHeight="1"/>
+    <row r="44" spans="1:1" ht="14.25" customHeight="1"/>
+    <row r="45" spans="1:1" ht="14.25" customHeight="1"/>
+    <row r="46" spans="1:1" ht="14.25" customHeight="1"/>
+    <row r="47" spans="1:1" ht="14.25" customHeight="1"/>
+    <row r="48" spans="1:1" ht="14.25" customHeight="1"/>
     <row r="49" ht="14.25" customHeight="1"/>
     <row r="50" ht="14.25" customHeight="1"/>
     <row r="51" ht="14.25" customHeight="1"/>
@@ -1803,6 +1843,9 @@
     <row r="1003" ht="14.25" customHeight="1"/>
     <row r="1004" ht="14.25" customHeight="1"/>
     <row r="1005" ht="14.25" customHeight="1"/>
+    <row r="1006" ht="14.25" customHeight="1"/>
+    <row r="1007" ht="14.25" customHeight="1"/>
+    <row r="1008" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Config_Test.xlsx
+++ b/Data/Config_Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github.com\rpapub\PurposefulPromethium\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94BE2D46-EB0A-4794-AABE-731D7779788D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB213B8-E1B0-4FFC-B3F3-5FABB3C91EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1095" yWindow="3540" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1095" yWindow="3540" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -1903,8 +1903,8 @@
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
-        <v>0</v>
+      <c r="B3" s="5">
+        <v>2</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>

--- a/Data/Config_Test.xlsx
+++ b/Data/Config_Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github.com\rpapub\PurposefulPromethium\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB213B8-E1B0-4FFC-B3F3-5FABB3C91EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21032C49-A2EC-43CC-98E5-79435C9DADE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1095" yWindow="3540" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9555" yWindow="2370" windowWidth="18270" windowHeight="11670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -117,9 +117,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>wildduck.email</t>
-  </si>
-  <si>
     <t>Imap_Server</t>
   </si>
   <si>
@@ -235,6 +232,9 @@
   </si>
   <si>
     <t>RPA/PurposefulPromethium/Testing/EndToEnd/successful/FormatB</t>
+  </si>
+  <si>
+    <t>mail.wildduck.email</t>
   </si>
 </sst>
 </file>
@@ -308,7 +308,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -324,7 +324,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -621,7 +621,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z1008"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.5703125" customWidth="1"/>
     <col min="2" max="2" width="43" style="5" customWidth="1"/>
@@ -676,10 +676,10 @@
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
       <c r="A3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>54</v>
       </c>
       <c r="C3" s="2"/>
     </row>
@@ -689,7 +689,7 @@
         <v>26</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>29</v>
@@ -698,27 +698,27 @@
     <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" t="s">
         <v>51</v>
-      </c>
-      <c r="C7" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" s="5">
         <v>993</v>
@@ -726,16 +726,16 @@
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
       <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B13" s="7">
         <v>10</v>
@@ -744,18 +744,18 @@
     <row r="14" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B16" s="5">
         <v>12</v>
@@ -763,7 +763,7 @@
     </row>
     <row r="17" spans="1:2" s="6" customFormat="1" ht="14.25" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B17" s="7">
         <v>0</v>
@@ -771,65 +771,65 @@
     </row>
     <row r="18" spans="1:2" ht="14.25" customHeight="1">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.25" customHeight="1">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:2" s="6" customFormat="1" ht="14.25" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:2" s="6" customFormat="1" ht="14.25" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:2" s="6" customFormat="1" ht="14.25" customHeight="1">
       <c r="A22" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="24" spans="1:2" ht="14.25" customHeight="1">
       <c r="A24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="26" spans="1:2" ht="14.25" customHeight="1">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="14.25" customHeight="1">
       <c r="A27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B27" s="5">
         <v>21</v>
@@ -837,35 +837,35 @@
     </row>
     <row r="28" spans="1:2" ht="14.25" customHeight="1">
       <c r="A28" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="14.25" customHeight="1">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="14.25" customHeight="1">
       <c r="A30" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>46</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="32" spans="1:2" ht="14.25" customHeight="1">
       <c r="A32" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="14.25" customHeight="1">
@@ -1856,7 +1856,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z988"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
     <col min="2" max="2" width="51" customWidth="1"/>
@@ -2964,7 +2964,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.85546875" customWidth="1"/>
     <col min="2" max="2" width="30.140625" customWidth="1"/>

--- a/Data/Config_Test.xlsx
+++ b/Data/Config_Test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github.com\rpapub\PurposefulPromethium\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB213B8-E1B0-4FFC-B3F3-5FABB3C91EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3FCCA6-1B70-42EE-989A-84753B758F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1095" yWindow="3540" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="13500" windowHeight="21285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -117,9 +117,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>wildduck.email</t>
-  </si>
-  <si>
     <t>Imap_Server</t>
   </si>
   <si>
@@ -189,9 +186,6 @@
     <t>OrchestratorFolderPath</t>
   </si>
   <si>
-    <t>ChapterEvents</t>
-  </si>
-  <si>
     <t>File_BasePathTemp</t>
   </si>
   <si>
@@ -235,6 +229,12 @@
   </si>
   <si>
     <t>RPA/PurposefulPromethium/Testing/EndToEnd/successful/FormatB</t>
+  </si>
+  <si>
+    <t>rpapub</t>
+  </si>
+  <si>
+    <t>mail.wildduck.email</t>
   </si>
 </sst>
 </file>
@@ -676,10 +676,10 @@
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="C3" s="2"/>
     </row>
@@ -689,7 +689,7 @@
         <v>26</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>29</v>
@@ -698,27 +698,27 @@
     <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" t="s">
         <v>51</v>
-      </c>
-      <c r="C7" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" s="5">
         <v>993</v>
@@ -726,16 +726,16 @@
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
       <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B13" s="7">
         <v>10</v>
@@ -744,18 +744,18 @@
     <row r="14" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B16" s="5">
         <v>12</v>
@@ -763,7 +763,7 @@
     </row>
     <row r="17" spans="1:2" s="6" customFormat="1" ht="14.25" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B17" s="7">
         <v>0</v>
@@ -771,65 +771,65 @@
     </row>
     <row r="18" spans="1:2" ht="14.25" customHeight="1">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.25" customHeight="1">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:2" s="6" customFormat="1" ht="14.25" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:2" s="6" customFormat="1" ht="14.25" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:2" s="6" customFormat="1" ht="14.25" customHeight="1">
       <c r="A22" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="24" spans="1:2" ht="14.25" customHeight="1">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="26" spans="1:2" ht="14.25" customHeight="1">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="14.25" customHeight="1">
       <c r="A27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B27" s="5">
         <v>21</v>
@@ -837,35 +837,35 @@
     </row>
     <row r="28" spans="1:2" ht="14.25" customHeight="1">
       <c r="A28" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="14.25" customHeight="1">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="14.25" customHeight="1">
       <c r="A30" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>46</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="32" spans="1:2" ht="14.25" customHeight="1">
       <c r="A32" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="14.25" customHeight="1">
